--- a/ansible/secureboot/secure_boot_report_robust.xlsx
+++ b/ansible/secureboot/secure_boot_report_robust.xlsx
@@ -8,17 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\openSUSE-Leap-15.6\home\jestebanl\Litocruz\ansible\secureboot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8A6A6D8-BFE0-49E9-809E-54CDD1D740E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1593962F-712A-4054-BB36-84883488620C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BDFF488B-0E21-4169-A5A0-FA31F8A32226}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" tabRatio="583" xr2:uid="{BDFF488B-0E21-4169-A5A0-FA31F8A32226}"/>
   </bookViews>
   <sheets>
-    <sheet name="secure_boot_report_robust" sheetId="1" r:id="rId1"/>
-    <sheet name="secure_boot_report_robust (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId3"/>
+    <sheet name="secure_boot_report_robust (2)" sheetId="3" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="DatosExternos_1" localSheetId="1" hidden="1">'secure_boot_report_robust (2)'!$A$1:$C$148</definedName>
+    <definedName name="DatosExternos_1" localSheetId="0" hidden="1">'secure_boot_report_robust (2)'!$A$1:$C$148</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -38,451 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="592" uniqueCount="305">
-  <si>
-    <t>hostname,secure_boot_status,check_method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">app-nnn, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">arum01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">bastion01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">bastion02, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">cisco-sySLog01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">codiasshSP02, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">commvaulT-frel.santpau.es, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dna-backUPs, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dns02, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dokuflex01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dokuflex01cons.santpau.es, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dwh01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dwh02, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dwh02des, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ritmocorE.santpau.es, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimtraCK01.santpau.es, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimtraCK01des.santpau.es, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">etccons01, unknown_efi , dmesg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">exhsp-prOXy-pass, enabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">famaafm02, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">famaafm02Des, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">foreman01, enabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">gestionlOGs, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">gestprj01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPEIWSTesT.santpau.es, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPEIDB01.santpau.es, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">informesDB01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">intrahsp01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">intrahsp02, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">intrahsp03, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">intranetHSp04, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ipquorum03, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">iptv01deS, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">jirahsp, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">jirahspbD-test, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mongodb, unknown_efi , dmesg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mongodb01, unknown_efi , dmesg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mongodb03, unknown_efi , dmesg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mongodb03Des, unknown_efi , dmesg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">moodle, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nagios.sANtpau.es, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nexus01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">openlab01Des, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">openlab08, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">patwindb02, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">patwindb02des, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">petitsacASa02, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">petitsacASa02des, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">pipdb, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">piqdb, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">proxypasS01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">puigsacaLM, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUENDAANblICK, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">redcapapP01, enabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">rman19, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapsolmaN01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapspa01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapspe, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapspf01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapspu01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sau01des, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">scannessUS01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sescli01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">setapp01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">setdb01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">smovil03, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">setdb01dES, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sonarqubE01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">spbdb, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">speas02, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">speas06, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">spedb, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">spudb, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">srv-web-APi-pifs, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sw-backuPS, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">taonet02, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tarif04, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">trak06deS, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBUNTU01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">webapps01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">webir01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">webpub01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">webpub02DEs, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">xicvar01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">zabbix01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">activiti01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">appwmp01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">atb01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">bbddspauA01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">codiasshSP01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dlab01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dns05, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dokuflex01test, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dwh01des, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">enigmaprN03, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">exhsp-prOXy-pass-int, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">famaapp01Des, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ftp01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">gefact02, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">gestioip, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">gitlab01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">gota04deS, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPEIXERo02.santpau.es, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">intrahsp01des, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">intrahsp04des, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">jenkins01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">jirahsp-TEst, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mirth02dES, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mongodb01Des, unknown_efi , dmesg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mongodb02, unknown_efi , dmesg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mongodb02Des, unknown_efi , dmesg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mongodb04Des, unknown_efi , dmesg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mongodbdES, unknown_efi , dmesg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">openlab01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">opsmanagER01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETITSACASA01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETITSACASA01DES, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">petitsacASa01des, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">piddb, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">pip01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">piq01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">proxy-paSS, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">proxy-paSS-ir, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">pyxisgr01.santpau.es, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">redcapdb01, enabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">redis01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapcconnECt01, unknown_efi , dmesg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapspb01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapspp01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sentry01, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">setapp01DEs, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">spadb, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">speas01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">speas04, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">speas05, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">spfdb, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sppdb, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">srv-db-sTOrage-pifs, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">susemanaGEr01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sycai01, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">trak03deS, bios_boot , stat_efi_dir </t>
-  </si>
-  <si>
-    <t xml:space="preserve">wdisp01pRO, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">webpub01DEs, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">webir02, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">webpub03, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">webpub04, disabled , mokutil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">developmENt03, bios_boot , stat_efi_dir </t>
-  </si>
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="464" uniqueCount="162">
   <si>
     <t>hostname</t>
   </si>
@@ -953,6 +508,21 @@
   </si>
   <si>
     <t>developmENt03</t>
+  </si>
+  <si>
+    <t>secure-boot status</t>
+  </si>
+  <si>
+    <t>ambiente</t>
+  </si>
+  <si>
+    <t>sistemas-produccion-correo</t>
+  </si>
+  <si>
+    <t>apps_dep_dev-other_linux</t>
+  </si>
+  <si>
+    <t>institut de recerca</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +665,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1275,8 +845,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <start/>
       <end/>
@@ -1391,6 +967,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <start style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </start>
+      <end/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <start/>
+      <end/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <start/>
+      <end style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </end>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1436,9 +1049,18 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1524,7 +1146,7 @@
   <autoFilter ref="A1:C148" xr:uid="{A1072D6F-9883-4151-92E0-CFD2462D628C}">
     <filterColumn colId="1">
       <filters>
-        <filter val="enabled"/>
+        <filter val="bios_boot"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1853,756 +1475,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D3F272-5202-4E56-8041-1565759BE3A5}">
-  <dimension ref="A1:A148"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>147</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B925A850-01A8-46D4-9230-0577FE8321FD}">
   <dimension ref="A1:C148"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2614,1630 +1486,1630 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>150</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>157</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>160</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>161</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>163</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>170</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>171</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>172</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>175</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>177</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>178</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>179</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>181</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>182</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>183</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>184</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>185</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>187</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>188</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>189</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>191</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>192</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>193</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>196</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>197</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>199</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>200</v>
+        <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>201</v>
+        <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>202</v>
+        <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>203</v>
+        <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>204</v>
+        <v>56</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>205</v>
+        <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>206</v>
+        <v>58</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>208</v>
+        <v>60</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>209</v>
+        <v>61</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>210</v>
+        <v>62</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>211</v>
+        <v>63</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>212</v>
+        <v>64</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>213</v>
+        <v>65</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>214</v>
+        <v>66</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>216</v>
+        <v>68</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>219</v>
+        <v>71</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>220</v>
+        <v>72</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>222</v>
+        <v>74</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>223</v>
+        <v>75</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>224</v>
+        <v>76</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>227</v>
+        <v>79</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>231</v>
+        <v>83</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>232</v>
+        <v>84</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>233</v>
+        <v>85</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>234</v>
+        <v>86</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>236</v>
+        <v>88</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>237</v>
+        <v>89</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>238</v>
+        <v>90</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>239</v>
+        <v>91</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>241</v>
+        <v>93</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>242</v>
+        <v>94</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>243</v>
+        <v>95</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>244</v>
+        <v>96</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>245</v>
+        <v>97</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>246</v>
+        <v>98</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>247</v>
+        <v>99</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>248</v>
+        <v>100</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>249</v>
+        <v>101</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>251</v>
+        <v>103</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>252</v>
+        <v>104</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>253</v>
+        <v>105</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>254</v>
+        <v>106</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>255</v>
+        <v>107</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>256</v>
+        <v>108</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>258</v>
+        <v>110</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>259</v>
+        <v>111</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>260</v>
+        <v>112</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>261</v>
+        <v>113</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>262</v>
+        <v>114</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>263</v>
+        <v>115</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>264</v>
+        <v>116</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>265</v>
+        <v>117</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>266</v>
+        <v>118</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>267</v>
+        <v>119</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>268</v>
+        <v>120</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>269</v>
+        <v>121</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>270</v>
+        <v>122</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>271</v>
+        <v>123</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>272</v>
+        <v>124</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>273</v>
+        <v>125</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>274</v>
+        <v>126</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>275</v>
+        <v>127</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>276</v>
+        <v>128</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>277</v>
+        <v>129</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>278</v>
+        <v>130</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>279</v>
+        <v>131</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>280</v>
+        <v>132</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>281</v>
+        <v>133</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>282</v>
+        <v>134</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>283</v>
+        <v>135</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>284</v>
+        <v>136</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>285</v>
+        <v>137</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>286</v>
+        <v>138</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>287</v>
+        <v>139</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>288</v>
+        <v>140</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>289</v>
+        <v>141</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>290</v>
+        <v>142</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>291</v>
+        <v>143</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>292</v>
+        <v>144</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>293</v>
+        <v>145</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>294</v>
+        <v>146</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>295</v>
+        <v>147</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>296</v>
+        <v>148</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>297</v>
+        <v>149</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>298</v>
+        <v>150</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>299</v>
+        <v>151</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>301</v>
+        <v>153</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>302</v>
+        <v>154</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>303</v>
+        <v>155</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4248,11 +3120,88 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82CE14A5-6574-4679-90D7-CF4BB8C71285}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="28.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
